--- a/Assets/StreamingAssets/story/11.xlsx
+++ b/Assets/StreamingAssets/story/11.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="14580" windowHeight="12585"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="78">
   <si>
     <t>名字</t>
   </si>
@@ -91,49 +91,178 @@
     <t>上次x3</t>
   </si>
   <si>
-    <t>张三</t>
+    <t>narrator</t>
+  </si>
+  <si>
+    <t>雨下了整整三个小时。</t>
+  </si>
+  <si>
+    <t>bk</t>
+  </si>
+  <si>
+    <t>乡间宅邸的壁灯忽明忽暗，像一双困倦却不肯闭上的眼睛。</t>
+  </si>
+  <si>
+    <t>铜制挂钟停在九点十七分，又在下一声滴答里继续向前。</t>
+  </si>
+  <si>
+    <t>雨水沿玻璃蜿蜒而下，把庭院里的玫瑰揉成一团模糊的暗红。</t>
+  </si>
+  <si>
+    <t>壁炉里只剩低伏的火，偶尔咬碎一截木炭。</t>
+  </si>
+  <si>
+    <t>长桌旁坐着四个人。没有人开口。</t>
+  </si>
+  <si>
+    <t>appearAt</t>
   </si>
   <si>
     <t>a</t>
   </si>
   <si>
-    <t>bk</t>
-  </si>
-  <si>
-    <t>appearAt</t>
-  </si>
-  <si>
     <t>b</t>
   </si>
   <si>
     <t>c</t>
   </si>
   <si>
-    <t>李四</t>
-  </si>
-  <si>
-    <t>disappear</t>
+    <t>你坐在桌子的这一端，面前只有一只深棕色皮革档案袋。</t>
   </si>
   <si>
     <t>moveTo</t>
   </si>
   <si>
+    <t>Arthur Bell靠在椅背上，领带打得一丝不苟。</t>
+  </si>
+  <si>
+    <t>他用食指敲着扶手，仿佛今晚只是一次无聊的聚会。</t>
+  </si>
+  <si>
+    <t>看够了吗？</t>
+  </si>
+  <si>
+    <t>Beatrice Hall坐得过分端正，只有交叠的手指出卖了颤抖。</t>
+  </si>
+  <si>
+    <t>我不知道你为什么把我们叫到这里。</t>
+  </si>
+  <si>
+    <t>Charles Reed坐在最远处，目光始终落在桌面的木纹上。</t>
+  </si>
+  <si>
+    <t>……</t>
+  </si>
+  <si>
+    <t>你把档案袋拉到面前。三道视线终于落在了同一个地方。</t>
+  </si>
+  <si>
     <t>u</t>
   </si>
   <si>
-    <t>choice</t>
-  </si>
-  <si>
-    <t>甲
-乙
-丙
-丁</t>
-  </si>
-  <si>
-    <t>111
-112
-113
-114</t>
+    <t>九点十七分。和她死去的时间一样。</t>
+  </si>
+  <si>
+    <t>你约我们来这里，就是为了翻旧账？</t>
+  </si>
+  <si>
+    <t>我以为我们早就达成共识了。</t>
+  </si>
+  <si>
+    <t>我和你们，可没有什么共识。</t>
+  </si>
+  <si>
+    <t>你的拇指压住金属扣。</t>
+  </si>
+  <si>
+    <t>“咔哒”一声，皮扣松开。</t>
+  </si>
+  <si>
+    <t>你从档案中抽出一张泛黄的照片，放在长桌中央。</t>
+  </si>
+  <si>
+    <t>照片里的Clara站在玫瑰丛前，笑得像那个夜晚永远不会到来。</t>
+  </si>
+  <si>
+    <t>Clara死前，见过你们三个人。</t>
+  </si>
+  <si>
+    <t>所以呢？见过我们，不等于我们杀了她。</t>
+  </si>
+  <si>
+    <t>我还没有说她是被杀的。</t>
+  </si>
+  <si>
+    <t>文字游戏。你还是只会这一套。</t>
+  </si>
+  <si>
+    <t>等一下……如果这是警方的调查，为什么没有警察？</t>
+  </si>
+  <si>
+    <t>又为什么偏偏是我们三个？</t>
+  </si>
+  <si>
+    <t>别装了，Beatrice。你收到消息时，可没有这么惊讶。</t>
+  </si>
+  <si>
+    <t>那条消息是你发的！你说Clara只是出了意外！</t>
+  </si>
+  <si>
+    <t>我说的是我看到的。至于后来发生了什么，你应该问Charles。</t>
+  </si>
+  <si>
+    <t>Charles？你后来又回去了？</t>
+  </si>
+  <si>
+    <t>Charles的鞋尖向后挪了半寸。</t>
+  </si>
+  <si>
+    <t>回答她。你不是最擅长替别人收拾残局吗？</t>
+  </si>
+  <si>
+    <t>你还是和以前一样。</t>
+  </si>
+  <si>
+    <t>system</t>
+  </si>
+  <si>
+    <t>（沉默）</t>
+  </si>
+  <si>
+    <t>够了。我们三个那晚都在场。</t>
+  </si>
+  <si>
+    <t>但最后一个离开的人，不是我。</t>
+  </si>
+  <si>
+    <t>你什么意思？</t>
+  </si>
+  <si>
+    <t>你翻开档案第一页。三个人同时安静下来。</t>
+  </si>
+  <si>
+    <t>嫌疑人状态已建立。</t>
+  </si>
+  <si>
+    <t>Arthur Bell。Beatrice Hall。Charles Reed。</t>
+  </si>
+  <si>
+    <t>今晚，我们不谈共识。只谈你们各自隐瞒的事实。</t>
+  </si>
+  <si>
+    <t>挂钟的分针越过刻度。</t>
+  </si>
+  <si>
+    <t>（钟声响起）</t>
+  </si>
+  <si>
+    <t>审讯开始。</t>
+  </si>
+  <si>
+    <t>A：Arthur Bell｜B：Beatrice Hall｜C：Charles Reed</t>
+  </si>
+  <si>
+    <t>EOF</t>
   </si>
 </sst>
 </file>
@@ -146,13 +275,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -299,7 +434,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -308,6 +443,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -493,12 +634,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -619,55 +775,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
@@ -682,78 +835,84 @@
     <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1067,7 +1226,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T26"/>
+  <dimension ref="A1:T50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -1132,224 +1291,188 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
-      <c r="A2" t="s">
+    <row r="2" ht="33" spans="1:20">
+      <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="C2" s="1"/>
       <c r="E2" t="s">
         <v>22</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+    </row>
+    <row r="3" ht="99" spans="1:20">
+      <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H2">
-        <v>100</v>
-      </c>
-      <c r="I2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2">
-        <v>-100</v>
-      </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R2" t="s">
-        <v>23</v>
-      </c>
-      <c r="S2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" t="s">
-        <v>27</v>
-      </c>
+      <c r="C3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
       <c r="M3" t="str">
         <f>IF(E2&lt;&gt;"",E2,M2)</f>
         <v>bk</v>
       </c>
       <c r="O3">
         <f>IF(H2&lt;&gt;"",H2,O2)</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <f>IF(K2&lt;&gt;"",K2,P2)</f>
-        <v>-100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
       <c r="T3">
         <f>IF(S2&lt;&gt;"",S2,T2)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20">
-      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="82.5" spans="1:20">
+      <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4">
-        <v>50</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="B4" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="C4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
       <c r="M4" t="str">
         <f t="shared" ref="M4:M25" si="0">IF(E3&lt;&gt;"",E3,M3)</f>
         <v>bk</v>
       </c>
       <c r="O4">
         <f t="shared" ref="O4:O25" si="1">IF(H3&lt;&gt;"",H3,O3)</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <f t="shared" ref="P4:P25" si="2">IF(K3&lt;&gt;"",K3,P3)</f>
-        <v>-100</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>25</v>
-      </c>
-      <c r="R4" t="s">
-        <v>28</v>
-      </c>
-      <c r="S4">
-        <v>-50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
       <c r="T4">
         <f t="shared" ref="T4:T25" si="3">IF(S3&lt;&gt;"",S3,T3)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20">
-      <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" t="s">
-        <v>27</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="99" spans="1:20">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
       <c r="M5" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O5">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="R5" t="s">
-        <v>27</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
       <c r="T5">
         <f t="shared" si="3"/>
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20">
-      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="66" spans="1:20">
+      <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6">
-        <v>100</v>
-      </c>
-      <c r="I6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6">
-        <v>-100</v>
-      </c>
-      <c r="L6" t="s">
-        <v>24</v>
-      </c>
+      <c r="B6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
       <c r="M6" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O6">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>25</v>
-      </c>
-      <c r="R6" t="s">
-        <v>23</v>
-      </c>
-      <c r="S6">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
       <c r="T6">
         <f t="shared" si="3"/>
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="49.5" spans="1:20">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>27</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="1">
+        <v>-448</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="M7" t="str">
         <f t="shared" si="0"/>
@@ -1357,753 +1480,1313 @@
       </c>
       <c r="O7">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <f t="shared" si="2"/>
-        <v>-100</v>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S7" s="1">
+        <v>448</v>
       </c>
       <c r="T7">
         <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20">
-      <c r="A8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="82.5" spans="1:20">
+      <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" t="s">
-        <v>28</v>
-      </c>
-      <c r="K8">
-        <v>50</v>
-      </c>
-      <c r="L8" t="s">
-        <v>24</v>
-      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="1">
+        <v>-450</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
       <c r="M8" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O8">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>-448</v>
       </c>
       <c r="P8">
         <f t="shared" si="2"/>
-        <v>-100</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>25</v>
-      </c>
-      <c r="R8" t="s">
-        <v>28</v>
-      </c>
-      <c r="S8">
-        <v>-50</v>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S8" s="1">
+        <v>450</v>
       </c>
       <c r="T8">
         <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" t="s">
-        <v>27</v>
-      </c>
+        <v>448</v>
+      </c>
+    </row>
+    <row r="9" ht="82.5" spans="1:20">
+      <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="1">
+        <v>-448</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
       <c r="M9" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O9">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>-450</v>
       </c>
       <c r="P9">
         <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="R9" t="s">
-        <v>27</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
       <c r="T9">
         <f t="shared" si="3"/>
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20">
-      <c r="A10" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="10" ht="82.5" spans="1:20">
+      <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B10">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10">
-        <v>100</v>
-      </c>
-      <c r="I10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10">
-        <v>-100</v>
-      </c>
-      <c r="L10" t="s">
-        <v>24</v>
-      </c>
+      <c r="B10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="1">
+        <v>-256</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
       <c r="M10" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O10">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>-448</v>
       </c>
       <c r="P10">
         <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>25</v>
-      </c>
-      <c r="R10" t="s">
-        <v>23</v>
-      </c>
-      <c r="S10">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
       <c r="T10">
         <f t="shared" si="3"/>
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11">
-        <v>10</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" t="s">
-        <v>27</v>
-      </c>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:20">
+      <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
       <c r="M11" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O11">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>-256</v>
       </c>
       <c r="P11">
         <f t="shared" si="2"/>
-        <v>-100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
       <c r="T11">
         <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20">
-      <c r="A12" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="12" ht="99" spans="1:20">
+      <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B12">
-        <v>11</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-      <c r="J12" t="s">
-        <v>28</v>
-      </c>
-      <c r="K12">
-        <v>50</v>
-      </c>
-      <c r="L12" t="s">
-        <v>24</v>
-      </c>
+      <c r="B12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="G12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="1">
+        <v>-448</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
       <c r="M12" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O12">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>-256</v>
       </c>
       <c r="P12">
         <f t="shared" si="2"/>
-        <v>-100</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>25</v>
-      </c>
-      <c r="R12" t="s">
-        <v>28</v>
-      </c>
-      <c r="S12">
-        <v>-50</v>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S12" s="1">
+        <v>448</v>
       </c>
       <c r="T12">
         <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" t="s">
-        <v>27</v>
-      </c>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="13" ht="66" spans="1:20">
+      <c r="A13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="1">
+        <v>-450</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
       <c r="M13" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O13">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>-448</v>
       </c>
       <c r="P13">
         <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="R13" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S13" s="1">
+        <v>450</v>
       </c>
       <c r="T13">
         <f t="shared" si="3"/>
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20">
-      <c r="A14" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="14" ht="99" spans="1:20">
+      <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B14">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14">
-        <v>100</v>
-      </c>
-      <c r="I14" t="s">
-        <v>21</v>
-      </c>
-      <c r="J14" t="s">
-        <v>23</v>
-      </c>
-      <c r="K14">
-        <v>-100</v>
-      </c>
-      <c r="L14" t="s">
-        <v>24</v>
-      </c>
+      <c r="B14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
       <c r="M14" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O14">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>-450</v>
       </c>
       <c r="P14">
         <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>25</v>
-      </c>
-      <c r="R14" t="s">
-        <v>23</v>
-      </c>
-      <c r="S14">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S14" s="1">
+        <v>448</v>
       </c>
       <c r="T14">
         <f t="shared" si="3"/>
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20">
-      <c r="A15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15">
-        <v>14</v>
-      </c>
-      <c r="C15" t="s">
-        <v>25</v>
-      </c>
-      <c r="G15" t="s">
-        <v>27</v>
-      </c>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:20">
+      <c r="A15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
       <c r="M15" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O15">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>-450</v>
       </c>
       <c r="P15">
         <f t="shared" si="2"/>
-        <v>-100</v>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S15" s="1">
+        <v>256</v>
       </c>
       <c r="T15">
         <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20">
-      <c r="A16" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="16" ht="82.5" spans="1:20">
+      <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B16">
-        <v>15</v>
-      </c>
-      <c r="C16" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" t="s">
-        <v>28</v>
-      </c>
-      <c r="K16">
-        <v>50</v>
-      </c>
-      <c r="L16" t="s">
-        <v>24</v>
-      </c>
+      <c r="B16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="G16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="1">
+        <v>-448</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
       <c r="M16" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O16">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>-450</v>
       </c>
       <c r="P16">
         <f t="shared" si="2"/>
-        <v>-100</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>25</v>
-      </c>
-      <c r="R16" t="s">
-        <v>28</v>
-      </c>
-      <c r="S16">
-        <v>-50</v>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S16" s="1">
+        <v>448</v>
       </c>
       <c r="T16">
         <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20">
-      <c r="A17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" t="s">
-        <v>27</v>
-      </c>
+        <v>256</v>
+      </c>
+    </row>
+    <row r="17" ht="66" spans="1:20">
+      <c r="A17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="1">
+        <v>-450</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
       <c r="M17" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O17">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>-448</v>
       </c>
       <c r="P17">
         <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="R17" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S17" s="1">
+        <v>450</v>
       </c>
       <c r="T17">
         <f t="shared" si="3"/>
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20">
-      <c r="A18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18">
-        <v>17</v>
-      </c>
-      <c r="C18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18">
-        <v>100</v>
-      </c>
-      <c r="I18" t="s">
-        <v>21</v>
-      </c>
-      <c r="J18" t="s">
-        <v>23</v>
-      </c>
-      <c r="K18">
-        <v>-100</v>
-      </c>
-      <c r="L18" t="s">
-        <v>24</v>
-      </c>
+        <v>448</v>
+      </c>
+    </row>
+    <row r="18" ht="66" spans="1:20">
+      <c r="A18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
       <c r="M18" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O18">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>-450</v>
       </c>
       <c r="P18">
         <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>25</v>
-      </c>
-      <c r="R18" t="s">
-        <v>23</v>
-      </c>
-      <c r="S18">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
       <c r="T18">
         <f t="shared" si="3"/>
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20">
-      <c r="A19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19">
-        <v>18</v>
-      </c>
-      <c r="C19" t="s">
-        <v>29</v>
-      </c>
-      <c r="G19" t="s">
-        <v>27</v>
-      </c>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="19" ht="49.5" spans="1:20">
+      <c r="A19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
       <c r="M19" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O19">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>-450</v>
       </c>
       <c r="P19">
         <f t="shared" si="2"/>
-        <v>-100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
       <c r="T19">
         <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20">
-        <v>19</v>
-      </c>
-      <c r="C20" t="s">
-        <v>29</v>
-      </c>
-      <c r="J20" t="s">
-        <v>28</v>
-      </c>
-      <c r="K20">
-        <v>50</v>
-      </c>
-      <c r="L20" t="s">
-        <v>24</v>
-      </c>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="20" ht="49.5" spans="1:20">
+      <c r="A20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
       <c r="M20" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O20">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>-450</v>
       </c>
       <c r="P20">
         <f t="shared" si="2"/>
-        <v>-100</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>25</v>
-      </c>
-      <c r="R20" t="s">
-        <v>28</v>
-      </c>
-      <c r="S20">
-        <v>-50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
       <c r="T20">
         <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20">
-      <c r="A21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="21" ht="33" spans="1:20">
+      <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C21" t="s">
-        <v>29</v>
-      </c>
-      <c r="J21" t="s">
-        <v>27</v>
-      </c>
+      <c r="B21" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
       <c r="M21" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O21">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>-450</v>
       </c>
       <c r="P21">
         <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="R21" t="s">
-        <v>27</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
       <c r="T21">
         <f t="shared" si="3"/>
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20">
-      <c r="A22" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="22" ht="49.5" spans="1:20">
+      <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B22">
-        <v>21</v>
-      </c>
-      <c r="C22" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22">
-        <v>100</v>
-      </c>
-      <c r="I22" t="s">
-        <v>21</v>
-      </c>
-      <c r="J22" t="s">
-        <v>23</v>
-      </c>
-      <c r="K22">
-        <v>-100</v>
-      </c>
-      <c r="L22" t="s">
-        <v>24</v>
-      </c>
+      <c r="B22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
       <c r="M22" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O22">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>-450</v>
       </c>
       <c r="P22">
         <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>25</v>
-      </c>
-      <c r="R22" t="s">
-        <v>23</v>
-      </c>
-      <c r="S22">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
       <c r="T22">
         <f t="shared" si="3"/>
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20">
-      <c r="A23" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23">
-        <v>22</v>
-      </c>
-      <c r="C23" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23" t="s">
-        <v>27</v>
-      </c>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="23" ht="82.5" spans="1:20">
+      <c r="A23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
       <c r="M23" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O23">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>-450</v>
       </c>
       <c r="P23">
         <f t="shared" si="2"/>
-        <v>-100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
       <c r="T23">
         <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20">
-      <c r="A24" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="24" ht="99" spans="1:20">
+      <c r="A24" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B24">
-        <v>23</v>
-      </c>
-      <c r="C24" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" t="s">
-        <v>28</v>
-      </c>
-      <c r="K24">
+      <c r="B24" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="L24" t="s">
-        <v>24</v>
-      </c>
+      <c r="C24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
       <c r="M24" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O24">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>-450</v>
       </c>
       <c r="P24">
         <f t="shared" si="2"/>
-        <v>-100</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>25</v>
-      </c>
-      <c r="R24" t="s">
-        <v>28</v>
-      </c>
-      <c r="S24">
-        <v>-50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
       <c r="T24">
         <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20">
-      <c r="A25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25">
-        <v>24</v>
-      </c>
-      <c r="C25" t="s">
-        <v>21</v>
-      </c>
-      <c r="J25" t="s">
-        <v>27</v>
-      </c>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="25" ht="49.5" spans="1:20">
+      <c r="A25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
       <c r="M25" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O25">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>-450</v>
       </c>
       <c r="P25">
         <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="R25" t="s">
-        <v>27</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
       <c r="T25">
         <f t="shared" si="3"/>
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="26" ht="54" spans="1:20">
-      <c r="A26" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="26" ht="66" spans="1:20">
+      <c r="A26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H26" s="1">
+        <v>-288</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+    </row>
+    <row r="27" ht="49.5" spans="1:20">
+      <c r="A27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+    </row>
+    <row r="28" ht="49.5" spans="1:20">
+      <c r="A28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+    </row>
+    <row r="29" ht="82.5" spans="1:20">
+      <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B29" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H29" s="1">
+        <v>-450</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+    </row>
+    <row r="30" ht="49.5" spans="1:20">
+      <c r="A30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
+    </row>
+    <row r="31" ht="82.5" spans="1:20">
+      <c r="A31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H31" s="1">
+        <v>-448</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="Q31" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="R31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S31" s="1">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="32" ht="82.5" spans="1:20">
+      <c r="A32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H32" s="1">
+        <v>-450</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K32" s="1">
+        <v>-112</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S32" s="1">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="33" ht="99" spans="1:19">
+      <c r="A33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+    </row>
+    <row r="34" ht="49.5" spans="1:19">
+      <c r="A34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+    </row>
+    <row r="35" ht="49.5" spans="1:19">
+      <c r="A35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="Q35" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S35" s="1">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="36" ht="66" spans="1:19">
+      <c r="A36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="Q36" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S36" s="1">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="37" ht="33" spans="1:19">
+      <c r="A37" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="1"/>
+    </row>
+    <row r="38" ht="16.5" spans="1:19">
+      <c r="A38" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="Q38" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R38" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S38" s="1">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="39" ht="49.5" spans="1:19">
+      <c r="A39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H39" s="1">
+        <v>-448</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="Q39" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S39" s="1">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="40" ht="49.5" spans="1:19">
+      <c r="A40" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H40" s="1">
+        <v>-450</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="Q40" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S40" s="1">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="41" ht="33" spans="1:19">
+      <c r="A41" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="Q41" s="1"/>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
+    </row>
+    <row r="42" ht="66" spans="1:19">
+      <c r="A42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="Q42" s="1"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
+    </row>
+    <row r="43" ht="33" spans="1:19">
+      <c r="A43" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="Q43" s="1"/>
+      <c r="R43" s="1"/>
+      <c r="S43" s="1"/>
+    </row>
+    <row r="44" ht="82.5" spans="1:19">
+      <c r="A44" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="1"/>
+    </row>
+    <row r="45" ht="82.5" spans="1:19">
+      <c r="A45" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
+    </row>
+    <row r="46" ht="33" spans="1:19">
+      <c r="A46" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="Q46" s="1"/>
+      <c r="R46" s="1"/>
+      <c r="S46" s="1"/>
+    </row>
+    <row r="47" ht="33" spans="1:19">
+      <c r="A47" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
+    </row>
+    <row r="48" ht="16.5" spans="1:19">
+      <c r="A48" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+      <c r="S48" s="1"/>
+    </row>
+    <row r="49" ht="99" spans="1:19">
+      <c r="A49" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C49" s="1"/>
+      <c r="G49" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H49" s="1">
+        <v>-450</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="Q49" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R49" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S49" s="1">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" spans="1:19">
+      <c r="A50" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
+      <c r="S50" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/StreamingAssets/story/11.xlsx
+++ b/Assets/StreamingAssets/story/11.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14580" windowHeight="12585"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="77">
   <si>
     <t>名字</t>
   </si>
@@ -257,9 +257,6 @@
   </si>
   <si>
     <t>审讯开始。</t>
-  </si>
-  <si>
-    <t>A：Arthur Bell｜B：Beatrice Hall｜C：Charles Reed</t>
   </si>
   <si>
     <t>EOF</t>
@@ -2750,39 +2747,25 @@
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
     </row>
-    <row r="49" ht="99" spans="1:19">
-      <c r="A49" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B49" s="2" t="s">
+    <row r="49" ht="16.5" spans="1:19">
+      <c r="A49" t="s">
         <v>76</v>
       </c>
+      <c r="B49" s="2"/>
       <c r="C49" s="1"/>
-      <c r="G49" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H49" s="1">
-        <v>-450</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
-      <c r="Q49" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="R49" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="S49" s="1">
-        <v>450</v>
-      </c>
+      <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
+      <c r="S49" s="1"/>
     </row>
     <row r="50" ht="16.5" spans="1:19">
       <c r="A50" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>

--- a/Assets/StreamingAssets/story/11.xlsx
+++ b/Assets/StreamingAssets/story/11.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="11895" windowHeight="5550"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="85">
   <si>
     <t>名字</t>
   </si>
@@ -100,15 +100,24 @@
     <t>bk</t>
   </si>
   <si>
+    <t>Amb_Rain_Loop</t>
+  </si>
+  <si>
     <t>乡间宅邸的壁灯忽明忽暗，像一双困倦却不肯闭上的眼睛。</t>
   </si>
   <si>
     <t>铜制挂钟停在九点十七分，又在下一声滴答里继续向前。</t>
   </si>
   <si>
+    <t>Amb_Clock_Tick</t>
+  </si>
+  <si>
     <t>雨水沿玻璃蜿蜒而下，把庭院里的玫瑰揉成一团模糊的暗红。</t>
   </si>
   <si>
+    <t>Amb_Thunderstorm</t>
+  </si>
+  <si>
     <t>壁炉里只剩低伏的火，偶尔咬碎一截木炭。</t>
   </si>
   <si>
@@ -157,6 +166,9 @@
     <t>你把档案袋拉到面前。三道视线终于落在了同一个地方。</t>
   </si>
   <si>
+    <t>BGM_Suspense_Loop</t>
+  </si>
+  <si>
     <t>u</t>
   </si>
   <si>
@@ -178,9 +190,15 @@
     <t>“咔哒”一声，皮扣松开。</t>
   </si>
   <si>
+    <t>UI_Flip_Card2</t>
+  </si>
+  <si>
     <t>你从档案中抽出一张泛黄的照片，放在长桌中央。</t>
   </si>
   <si>
+    <t>UI_Flip_Card1</t>
+  </si>
+  <si>
     <t>照片里的Clara站在玫瑰丛前，笑得像那个夜晚永远不会到来。</t>
   </si>
   <si>
@@ -217,6 +235,9 @@
     <t>Charles的鞋尖向后挪了半寸。</t>
   </si>
   <si>
+    <t>UI_Stamp</t>
+  </si>
+  <si>
     <t>回答她。你不是最擅长替别人收拾残局吗？</t>
   </si>
   <si>
@@ -241,12 +262,12 @@
     <t>你翻开档案第一页。三个人同时安静下来。</t>
   </si>
   <si>
+    <t>UI_Page_Turn1</t>
+  </si>
+  <si>
     <t>嫌疑人状态已建立。</t>
   </si>
   <si>
-    <t>Arthur Bell。Beatrice Hall。Charles Reed。</t>
-  </si>
-  <si>
     <t>今晚，我们不谈共识。只谈你们各自隐瞒的事实。</t>
   </si>
   <si>
@@ -254,6 +275,9 @@
   </si>
   <si>
     <t>（钟声响起）</t>
+  </si>
+  <si>
+    <t>SFX_Clock_Oneshot</t>
   </si>
   <si>
     <t>审讯开始。</t>
@@ -272,7 +296,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -284,6 +308,12 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -772,137 +802,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -910,6 +940,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1299,6 +1335,9 @@
       <c r="E2" t="s">
         <v>22</v>
       </c>
+      <c r="F2" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -1314,9 +1353,11 @@
         <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1"/>
+      <c r="D3" s="4"/>
+      <c r="F3" s="4"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -1348,9 +1389,13 @@
         <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1"/>
+      <c r="D4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="4"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -1382,9 +1427,13 @@
         <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" s="1"/>
+      <c r="D5" s="4"/>
+      <c r="F5" s="4" t="s">
+        <v>28</v>
+      </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -1416,9 +1465,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C6" s="1"/>
+      <c r="D6" s="4"/>
+      <c r="F6" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -1450,26 +1503,28 @@
         <v>20</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C7" s="1"/>
+      <c r="D7" s="4"/>
+      <c r="F7" s="4"/>
       <c r="G7" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H7" s="1">
         <v>-448</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K7" s="1">
         <v>0</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M7" t="str">
         <f t="shared" si="0"/>
@@ -1484,10 +1539,10 @@
         <v>0</v>
       </c>
       <c r="Q7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="R7" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="S7" s="1">
         <v>448</v>
@@ -1502,17 +1557,18 @@
         <v>20</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C8" s="1"/>
+      <c r="D8" s="3"/>
       <c r="G8" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H8" s="1">
         <v>-450</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1530,10 +1586,10 @@
         <v>0</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S8" s="1">
         <v>450</v>
@@ -1548,17 +1604,18 @@
         <v>20</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C9" s="1"/>
+      <c r="D9" s="3"/>
       <c r="G9" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H9" s="1">
         <v>-448</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1588,17 +1645,18 @@
         <v>20</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" s="1"/>
+      <c r="D10" s="3"/>
       <c r="G10" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H10" s="1">
         <v>-256</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -1625,14 +1683,15 @@
     </row>
     <row r="11" ht="16.5" spans="1:20">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="D11" s="3"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -1664,17 +1723,18 @@
         <v>20</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C12" s="1"/>
+      <c r="D12" s="3"/>
       <c r="G12" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H12" s="1">
         <v>-448</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1692,10 +1752,10 @@
         <v>0</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S12" s="1">
         <v>448</v>
@@ -1707,22 +1767,23 @@
     </row>
     <row r="13" ht="66" spans="1:20">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D13" s="3"/>
       <c r="G13" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H13" s="1">
         <v>-450</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1740,10 +1801,10 @@
         <v>0</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S13" s="1">
         <v>450</v>
@@ -1758,9 +1819,10 @@
         <v>20</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C14" s="1"/>
+      <c r="D14" s="3"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -1780,10 +1842,10 @@
         <v>0</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S14" s="1">
         <v>448</v>
@@ -1795,14 +1857,15 @@
     </row>
     <row r="15" ht="16.5" spans="1:20">
       <c r="A15" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="D15" s="3"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -1822,10 +1885,10 @@
         <v>0</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S15" s="1">
         <v>256</v>
@@ -1840,17 +1903,21 @@
         <v>20</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1"/>
+      <c r="D16" s="3"/>
+      <c r="F16" t="s">
+        <v>45</v>
+      </c>
       <c r="G16" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H16" s="1">
         <v>-448</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1868,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S16" s="1">
         <v>448</v>
@@ -1883,22 +1950,23 @@
     </row>
     <row r="17" ht="66" spans="1:20">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>42</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="D17" s="4"/>
       <c r="G17" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H17" s="1">
         <v>-450</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1916,10 +1984,10 @@
         <v>0</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S17" s="1">
         <v>450</v>
@@ -1931,14 +1999,15 @@
     </row>
     <row r="18" ht="66" spans="1:20">
       <c r="A18" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="D18" s="3"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1967,14 +2036,15 @@
     </row>
     <row r="19" ht="49.5" spans="1:20">
       <c r="A19" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="D19" s="3"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -2003,14 +2073,15 @@
     </row>
     <row r="20" ht="49.5" spans="1:20">
       <c r="A20" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="D20" s="3"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -2042,9 +2113,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1"/>
+      <c r="D21" s="3"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -2076,9 +2148,12 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C22" s="1"/>
+      <c r="D22" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -2110,9 +2185,12 @@
         <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C23" s="1"/>
+      <c r="D23" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -2144,9 +2222,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C24" s="1"/>
+      <c r="D24" s="3"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -2175,14 +2254,15 @@
     </row>
     <row r="25" ht="49.5" spans="1:20">
       <c r="A25" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>42</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="D25" s="3"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -2211,22 +2291,23 @@
     </row>
     <row r="26" ht="66" spans="1:20">
       <c r="A26" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="D26" s="3"/>
       <c r="G26" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H26" s="1">
         <v>-288</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -2237,14 +2318,15 @@
     </row>
     <row r="27" ht="49.5" spans="1:20">
       <c r="A27" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>42</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="D27" s="3"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -2257,14 +2339,15 @@
     </row>
     <row r="28" ht="49.5" spans="1:20">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="D28" s="3"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -2277,22 +2360,23 @@
     </row>
     <row r="29" ht="82.5" spans="1:20">
       <c r="A29" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D29" s="3"/>
       <c r="G29" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H29" s="1">
         <v>-450</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
@@ -2303,14 +2387,15 @@
     </row>
     <row r="30" ht="49.5" spans="1:20">
       <c r="A30" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D30" s="3"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -2323,31 +2408,32 @@
     </row>
     <row r="31" ht="82.5" spans="1:20">
       <c r="A31" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="D31" s="3"/>
       <c r="G31" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H31" s="1">
         <v>-448</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="Q31" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S31" s="1">
         <v>448</v>
@@ -2355,37 +2441,38 @@
     </row>
     <row r="32" ht="82.5" spans="1:20">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D32" s="4"/>
       <c r="G32" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H32" s="1">
         <v>-450</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K32" s="1">
         <v>-112</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S32" s="1">
         <v>450</v>
@@ -2393,25 +2480,26 @@
     </row>
     <row r="33" ht="99" spans="1:19">
       <c r="A33" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="D33" s="3"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="K33" s="1">
-        <v>0</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
@@ -2419,14 +2507,15 @@
     </row>
     <row r="34" ht="49.5" spans="1:19">
       <c r="A34" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D34" s="3"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -2442,9 +2531,12 @@
         <v>20</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C35" s="1"/>
+      <c r="D35" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -2452,10 +2544,10 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="Q35" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S35" s="1">
         <v>448</v>
@@ -2463,14 +2555,15 @@
     </row>
     <row r="36" ht="66" spans="1:19">
       <c r="A36" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="D36" s="3"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -2478,10 +2571,10 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="Q36" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S36" s="1">
         <v>512</v>
@@ -2489,14 +2582,15 @@
     </row>
     <row r="37" ht="33" spans="1:19">
       <c r="A37" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="D37" s="3"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -2507,14 +2601,17 @@
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
     </row>
-    <row r="38" ht="16.5" spans="1:19">
+    <row r="38" ht="27" spans="1:19">
       <c r="A38" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C38" s="1"/>
+      <c r="D38" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -2522,10 +2619,10 @@
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="Q38" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S38" s="1">
         <v>256</v>
@@ -2533,31 +2630,32 @@
     </row>
     <row r="39" ht="49.5" spans="1:19">
       <c r="A39" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="D39" s="3"/>
       <c r="G39" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H39" s="1">
         <v>-448</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="Q39" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S39" s="1">
         <v>448</v>
@@ -2565,31 +2663,32 @@
     </row>
     <row r="40" ht="49.5" spans="1:19">
       <c r="A40" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="D40" s="3"/>
       <c r="G40" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H40" s="1">
         <v>-450</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="Q40" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S40" s="1">
         <v>450</v>
@@ -2597,14 +2696,15 @@
     </row>
     <row r="41" ht="33" spans="1:19">
       <c r="A41" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D41" s="3"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -2620,9 +2720,12 @@
         <v>20</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C42" s="1"/>
+      <c r="D42" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -2635,12 +2738,13 @@
     </row>
     <row r="43" ht="33" spans="1:19">
       <c r="A43" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C43" s="1"/>
+      <c r="D43" s="3"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -2653,14 +2757,15 @@
     </row>
     <row r="44" ht="82.5" spans="1:19">
       <c r="A44" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>42</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="D44" s="3"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -2671,15 +2776,16 @@
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
     </row>
-    <row r="45" ht="82.5" spans="1:19">
+    <row r="45" ht="33" spans="1:19">
       <c r="A45" s="1" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>42</v>
+        <v>80</v>
+      </c>
+      <c r="C45" s="1"/>
+      <c r="D45" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
@@ -2693,12 +2799,15 @@
     </row>
     <row r="46" ht="33" spans="1:19">
       <c r="A46" s="1" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C46" s="1"/>
+      <c r="D46" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -2709,14 +2818,17 @@
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
     </row>
-    <row r="47" ht="33" spans="1:19">
+    <row r="47" ht="16.5" spans="1:19">
       <c r="A47" s="1" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C47" s="1"/>
+        <v>83</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D47" s="3"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -2728,15 +2840,12 @@
       <c r="S47" s="1"/>
     </row>
     <row r="48" ht="16.5" spans="1:19">
-      <c r="A48" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="A48" t="s">
+        <v>84</v>
+      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="3"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -2749,10 +2858,8 @@
     </row>
     <row r="49" ht="16.5" spans="1:19">
       <c r="A49" t="s">
-        <v>76</v>
-      </c>
-      <c r="B49" s="2"/>
-      <c r="C49" s="1"/>
+        <v>84</v>
+      </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -2765,7 +2872,7 @@
     </row>
     <row r="50" ht="16.5" spans="1:19">
       <c r="A50" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>

--- a/Assets/StreamingAssets/story/11.xlsx
+++ b/Assets/StreamingAssets/story/11.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11895" windowHeight="5550"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="91">
   <si>
     <t>名字</t>
   </si>
@@ -103,6 +103,15 @@
     <t>Amb_Rain_Loop</t>
   </si>
   <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
     <t>乡间宅邸的壁灯忽明忽暗，像一双困倦却不肯闭上的眼睛。</t>
   </si>
   <si>
@@ -127,30 +136,24 @@
     <t>appearAt</t>
   </si>
   <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
     <t>你坐在桌子的这一端，面前只有一只深棕色皮革档案袋。</t>
   </si>
   <si>
+    <t>Arthur Bell靠在椅背上，领带打得一丝不苟。</t>
+  </si>
+  <si>
+    <t>a2</t>
+  </si>
+  <si>
+    <t>他用食指敲着扶手，仿佛今晚只是一次无聊的聚会。</t>
+  </si>
+  <si>
+    <t>看够了吗？</t>
+  </si>
+  <si>
     <t>moveTo</t>
   </si>
   <si>
-    <t>Arthur Bell靠在椅背上，领带打得一丝不苟。</t>
-  </si>
-  <si>
-    <t>他用食指敲着扶手，仿佛今晚只是一次无聊的聚会。</t>
-  </si>
-  <si>
-    <t>看够了吗？</t>
-  </si>
-  <si>
     <t>Beatrice Hall坐得过分端正，只有交叠的手指出卖了颤抖。</t>
   </si>
   <si>
@@ -160,6 +163,9 @@
     <t>Charles Reed坐在最远处，目光始终落在桌面的木纹上。</t>
   </si>
   <si>
+    <t>c2</t>
+  </si>
+  <si>
     <t>……</t>
   </si>
   <si>
@@ -199,7 +205,13 @@
     <t>UI_Flip_Card1</t>
   </si>
   <si>
-    <t>照片里的Clara站在玫瑰丛前，笑得像那个夜晚永远不会到来。</t>
+    <t>证据</t>
+  </si>
+  <si>
+    <t>dead</t>
+  </si>
+  <si>
+    <t>照片里的 Clara 静静站着，垂落的黑发遮住了大半张脸。她微抿着唇，仿佛早已预感到那个夜晚终会到来。</t>
   </si>
   <si>
     <t>Clara死前，见过你们三个人。</t>
@@ -232,10 +244,16 @@
     <t>Charles？你后来又回去了？</t>
   </si>
   <si>
+    <t>b2</t>
+  </si>
+  <si>
     <t>Charles的鞋尖向后挪了半寸。</t>
   </si>
   <si>
     <t>UI_Stamp</t>
+  </si>
+  <si>
+    <t>c3</t>
   </si>
   <si>
     <t>回答她。你不是最擅长替别人收拾残局吗？</t>
@@ -1340,11 +1358,17 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="Q2" s="1"/>
+      <c r="L2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
     </row>
@@ -1353,17 +1377,21 @@
         <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
+      <c r="I3" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
+      <c r="L3" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M3" t="str">
         <f>IF(E2&lt;&gt;"",E2,M2)</f>
         <v>bk</v>
@@ -1376,7 +1404,9 @@
         <f>IF(K2&lt;&gt;"",K2,P2)</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="1"/>
+      <c r="Q3" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3">
@@ -1389,19 +1419,23 @@
         <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
+      <c r="I4" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
+      <c r="L4" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M4" t="str">
         <f t="shared" ref="M4:M25" si="0">IF(E3&lt;&gt;"",E3,M3)</f>
         <v>bk</v>
@@ -1414,7 +1448,9 @@
         <f t="shared" ref="P4:P25" si="2">IF(K3&lt;&gt;"",K3,P3)</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="1"/>
+      <c r="Q4" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4">
@@ -1427,19 +1463,23 @@
         <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="4"/>
       <c r="F5" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="L5" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M5" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
@@ -1452,7 +1492,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q5" s="1"/>
+      <c r="Q5" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5">
@@ -1465,7 +1507,7 @@
         <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="4"/>
@@ -1474,10 +1516,14 @@
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+      <c r="I6" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
+      <c r="L6" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M6" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
@@ -1490,7 +1536,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q6" s="1"/>
+      <c r="Q6" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6">
@@ -1503,28 +1551,28 @@
         <v>20</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H7" s="1">
-        <v>-448</v>
+        <v>-650</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="M7" t="str">
         <f t="shared" si="0"/>
@@ -1539,13 +1587,13 @@
         <v>0</v>
       </c>
       <c r="Q7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="R7" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="S7" s="1">
-        <v>448</v>
+        <v>650</v>
       </c>
       <c r="T7">
         <f t="shared" si="3"/>
@@ -1561,42 +1609,36 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="3"/>
-      <c r="G8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" s="1">
-        <v>-450</v>
-      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
+      <c r="L8" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M8" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O8">
         <f t="shared" si="1"/>
-        <v>-448</v>
+        <v>-650</v>
       </c>
       <c r="P8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S8" s="1">
-        <v>450</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
       <c r="T8">
         <f t="shared" si="3"/>
-        <v>448</v>
+        <v>650</v>
       </c>
     </row>
     <row r="9" ht="82.5" spans="1:20">
@@ -1604,40 +1646,40 @@
         <v>20</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="3"/>
-      <c r="G9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" s="1">
-        <v>-448</v>
-      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
       <c r="I9" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
+      <c r="L9" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M9" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O9">
         <f t="shared" si="1"/>
-        <v>-450</v>
+        <v>-650</v>
       </c>
       <c r="P9">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9">
         <f t="shared" si="3"/>
-        <v>450</v>
+        <v>650</v>
       </c>
     </row>
     <row r="10" ht="82.5" spans="1:20">
@@ -1649,73 +1691,83 @@
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="3"/>
-      <c r="G10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H10" s="1">
-        <v>-256</v>
-      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
       <c r="I10" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
+      <c r="L10" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M10" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O10">
         <f t="shared" si="1"/>
-        <v>-448</v>
+        <v>-650</v>
       </c>
       <c r="P10">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10">
         <f t="shared" si="3"/>
-        <v>450</v>
+        <v>650</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:20">
       <c r="A11" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+      <c r="G11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="1">
+        <v>-650</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
+      <c r="L11" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M11" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O11">
         <f t="shared" si="1"/>
-        <v>-256</v>
+        <v>-650</v>
       </c>
       <c r="P11">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11">
         <f t="shared" si="3"/>
-        <v>450</v>
+        <v>650</v>
       </c>
     </row>
     <row r="12" ht="99" spans="1:20">
@@ -1723,95 +1775,87 @@
         <v>20</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="3"/>
       <c r="G12" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H12" s="1">
-        <v>-448</v>
+        <v>-650</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
+      <c r="L12" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M12" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O12">
         <f t="shared" si="1"/>
-        <v>-256</v>
+        <v>-650</v>
       </c>
       <c r="P12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S12" s="1">
-        <v>448</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
       <c r="T12">
         <f t="shared" si="3"/>
-        <v>450</v>
+        <v>650</v>
       </c>
     </row>
     <row r="13" ht="66" spans="1:20">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="G13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" s="1">
-        <v>-450</v>
-      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
       <c r="I13" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
+      <c r="L13" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M13" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O13">
         <f t="shared" si="1"/>
-        <v>-448</v>
+        <v>-650</v>
       </c>
       <c r="P13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S13" s="1">
-        <v>450</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
       <c r="T13">
         <f t="shared" si="3"/>
-        <v>448</v>
+        <v>650</v>
       </c>
     </row>
     <row r="14" ht="99" spans="1:20">
@@ -1819,83 +1863,87 @@
         <v>20</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="3"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="I14" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
+      <c r="L14" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M14" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O14">
         <f t="shared" si="1"/>
-        <v>-450</v>
+        <v>-650</v>
       </c>
       <c r="P14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="S14" s="1">
-        <v>448</v>
+        <v>650</v>
       </c>
       <c r="T14">
         <f t="shared" si="3"/>
-        <v>450</v>
+        <v>650</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:20">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D15" s="3"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="I15" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
+      <c r="L15" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M15" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O15">
         <f t="shared" si="1"/>
-        <v>-450</v>
+        <v>-650</v>
       </c>
       <c r="P15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S15" s="1">
-        <v>256</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="3"/>
-        <v>448</v>
+        <v>44</v>
+      </c>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" t="e">
+        <f>IF(#REF!&lt;&gt;"",#REF!,T14)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="16" ht="82.5" spans="1:20">
@@ -1903,209 +1951,217 @@
         <v>20</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="3"/>
       <c r="F16" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H16" s="1">
-        <v>-448</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
       <c r="I16" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
+      <c r="L16" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M16" t="str">
         <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O16">
         <f t="shared" si="1"/>
-        <v>-450</v>
+        <v>-650</v>
       </c>
       <c r="P16">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S16" s="1">
-        <v>448</v>
+        <v>44</v>
       </c>
       <c r="T16">
-        <f t="shared" si="3"/>
-        <v>256</v>
+        <f>IF(S14&lt;&gt;"",S14,T15)</f>
+        <v>650</v>
       </c>
     </row>
     <row r="17" ht="66" spans="1:20">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D17" s="4"/>
-      <c r="G17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" s="1">
-        <v>-450</v>
-      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
       <c r="I17" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
+      <c r="L17" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M17" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E16&lt;&gt;"",E16,M16)</f>
         <v>bk</v>
       </c>
       <c r="O17">
-        <f t="shared" si="1"/>
-        <v>-448</v>
+        <f>IF(H16&lt;&gt;"",H16,O16)</f>
+        <v>-650</v>
       </c>
       <c r="P17">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>IF(K16&lt;&gt;"",K16,P16)</f>
+        <v>100</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="S17" s="1">
-        <v>450</v>
+        <v>650</v>
       </c>
       <c r="T17">
-        <f t="shared" si="3"/>
-        <v>448</v>
+        <f>IF(S15&lt;&gt;"",S15,T16)</f>
+        <v>650</v>
       </c>
     </row>
     <row r="18" ht="66" spans="1:20">
       <c r="A18" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D18" s="3"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
+      <c r="I18" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
+      <c r="L18" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M18" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="M18:M23" si="4">IF(E17&lt;&gt;"",E17,M17)</f>
         <v>bk</v>
       </c>
       <c r="O18">
-        <f t="shared" si="1"/>
-        <v>-450</v>
+        <f t="shared" ref="O18:O23" si="5">IF(H17&lt;&gt;"",H17,O17)</f>
+        <v>-650</v>
       </c>
       <c r="P18">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="1"/>
+        <f t="shared" ref="P18:P23" si="6">IF(K17&lt;&gt;"",K17,P17)</f>
+        <v>100</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18">
-        <f t="shared" si="3"/>
-        <v>450</v>
+        <f t="shared" ref="T18:T23" si="7">IF(S17&lt;&gt;"",S17,T17)</f>
+        <v>650</v>
       </c>
     </row>
     <row r="19" ht="49.5" spans="1:20">
       <c r="A19" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D19" s="3"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
+      <c r="I19" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
+      <c r="L19" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M19" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>bk</v>
       </c>
       <c r="O19">
-        <f t="shared" si="1"/>
-        <v>-450</v>
+        <f t="shared" si="5"/>
+        <v>-650</v>
       </c>
       <c r="P19">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="1"/>
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19">
-        <f t="shared" si="3"/>
-        <v>450</v>
+        <f t="shared" si="7"/>
+        <v>650</v>
       </c>
     </row>
     <row r="20" ht="49.5" spans="1:20">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D20" s="3"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
+      <c r="I20" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
+      <c r="L20" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>bk</v>
       </c>
       <c r="O20">
-        <f t="shared" si="1"/>
-        <v>-450</v>
+        <f t="shared" si="5"/>
+        <v>-650</v>
       </c>
       <c r="P20">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="1"/>
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20">
-        <f t="shared" si="3"/>
-        <v>450</v>
+        <f t="shared" si="7"/>
+        <v>650</v>
       </c>
     </row>
     <row r="21" ht="33" spans="1:20">
@@ -2113,34 +2169,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="3"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
+      <c r="I21" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
+      <c r="L21" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M21" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>bk</v>
       </c>
       <c r="O21">
-        <f t="shared" si="1"/>
-        <v>-450</v>
+        <f t="shared" si="5"/>
+        <v>-650</v>
       </c>
       <c r="P21">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="1"/>
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
       <c r="T21">
-        <f t="shared" si="3"/>
-        <v>450</v>
+        <f t="shared" si="7"/>
+        <v>650</v>
       </c>
     </row>
     <row r="22" ht="49.5" spans="1:20">
@@ -2148,36 +2210,42 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
+      <c r="I22" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
+      <c r="L22" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M22" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>bk</v>
       </c>
       <c r="O22">
-        <f t="shared" si="1"/>
-        <v>-450</v>
+        <f t="shared" si="5"/>
+        <v>-650</v>
       </c>
       <c r="P22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="1"/>
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
       <c r="T22">
-        <f t="shared" si="3"/>
-        <v>450</v>
+        <f t="shared" si="7"/>
+        <v>650</v>
       </c>
     </row>
     <row r="23" ht="82.5" spans="1:20">
@@ -2185,666 +2253,743 @@
         <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
+      <c r="I23" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>bk</v>
       </c>
       <c r="O23">
-        <f t="shared" si="1"/>
-        <v>-450</v>
+        <f t="shared" si="5"/>
+        <v>-650</v>
       </c>
       <c r="P23">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="1"/>
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
       <c r="T23">
-        <f t="shared" si="3"/>
-        <v>450</v>
-      </c>
-    </row>
-    <row r="24" ht="99" spans="1:20">
-      <c r="A24" s="1" t="s">
+        <f t="shared" si="7"/>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20">
+      <c r="A24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" ht="165" spans="1:20">
+      <c r="A25" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="3"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" t="str">
-        <f t="shared" si="0"/>
-        <v>bk</v>
-      </c>
-      <c r="O24">
-        <f t="shared" si="1"/>
-        <v>-450</v>
-      </c>
-      <c r="P24">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24">
-        <f t="shared" si="3"/>
-        <v>450</v>
-      </c>
-    </row>
-    <row r="25" ht="49.5" spans="1:20">
-      <c r="A25" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="B25" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>46</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="C25" s="1"/>
       <c r="D25" s="3"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
+      <c r="I25" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
+      <c r="L25" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="M25" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(E23&lt;&gt;"",E23,M23)</f>
         <v>bk</v>
       </c>
       <c r="O25">
-        <f t="shared" si="1"/>
-        <v>-450</v>
+        <f>IF(H23&lt;&gt;"",H23,O23)</f>
+        <v>-650</v>
       </c>
       <c r="P25">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="1"/>
+        <f>IF(K23&lt;&gt;"",K23,P23)</f>
+        <v>100</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25">
-        <f t="shared" si="3"/>
-        <v>450</v>
-      </c>
-    </row>
-    <row r="26" ht="66" spans="1:20">
+        <f>IF(S23&lt;&gt;"",S23,T23)</f>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="26" ht="49.5" spans="1:20">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D26" s="3"/>
-      <c r="G26" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H26" s="1">
-        <v>-288</v>
-      </c>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
       <c r="I26" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="Q26" s="1"/>
+      <c r="L26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M26" t="str">
+        <f>IF(E25&lt;&gt;"",E25,M25)</f>
+        <v>bk</v>
+      </c>
+      <c r="O26">
+        <f>IF(H25&lt;&gt;"",H25,O25)</f>
+        <v>-650</v>
+      </c>
+      <c r="P26">
+        <f>IF(K25&lt;&gt;"",K25,P25)</f>
+        <v>100</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
-    </row>
-    <row r="27" ht="49.5" spans="1:20">
+      <c r="T26">
+        <f>IF(S25&lt;&gt;"",S25,T25)</f>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="27" ht="66" spans="1:20">
       <c r="A27" s="1" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="D27" s="3"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
+      <c r="I27" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="Q27" s="1"/>
+      <c r="L27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
     </row>
     <row r="28" ht="49.5" spans="1:20">
       <c r="A28" s="1" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D28" s="3"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
+      <c r="I28" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="Q28" s="1"/>
+      <c r="L28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
     </row>
-    <row r="29" ht="82.5" spans="1:20">
+    <row r="29" ht="49.5" spans="1:20">
       <c r="A29" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D29" s="3"/>
       <c r="G29" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H29" s="1">
-        <v>-450</v>
+        <v>-650</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="Q29" s="1"/>
+      <c r="L29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
     </row>
-    <row r="30" ht="49.5" spans="1:20">
+    <row r="30" ht="82.5" spans="1:20">
       <c r="A30" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D30" s="3"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
+      <c r="I30" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="Q30" s="1"/>
+      <c r="L30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
     </row>
-    <row r="31" ht="82.5" spans="1:20">
+    <row r="31" ht="49.5" spans="1:20">
       <c r="A31" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D31" s="3"/>
-      <c r="G31" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H31" s="1">
-        <v>-448</v>
-      </c>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
       <c r="I31" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
+      <c r="L31" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="Q31" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="R31" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S31" s="1">
-        <v>448</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
     </row>
     <row r="32" ht="82.5" spans="1:20">
       <c r="A32" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32" s="4"/>
-      <c r="G32" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H32" s="1">
-        <v>-450</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
       <c r="I32" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K32" s="1">
-        <v>-112</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
       <c r="L32" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="R32" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S32" s="1">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="33" ht="99" spans="1:19">
+        <v>26</v>
+      </c>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+    </row>
+    <row r="33" ht="82.5" spans="1:19">
       <c r="A33" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="D33" s="4"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
+      <c r="I33" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="J33" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K33" s="1">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q33" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
     </row>
-    <row r="34" ht="49.5" spans="1:19">
+    <row r="34" ht="99" spans="1:19">
       <c r="A34" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D34" s="3"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="Q34" s="1"/>
+      <c r="G34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H34" s="1">
+        <v>-650</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K34" s="1">
+        <v>100</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
     </row>
     <row r="35" ht="49.5" spans="1:19">
       <c r="A35" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="3" t="s">
-        <v>68</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" s="3"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
+      <c r="I35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K35" s="1">
+        <v>100</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="Q35" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="R35" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S35" s="1">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="36" ht="66" spans="1:19">
+        <v>26</v>
+      </c>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+    </row>
+    <row r="36" ht="49.5" spans="1:19">
       <c r="A36" s="1" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D36" s="3"/>
+        <v>72</v>
+      </c>
+      <c r="C36" s="1"/>
+      <c r="D36" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
+      <c r="I36" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
+      <c r="L36" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="Q36" s="1" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="S36" s="1">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="37" ht="33" spans="1:19">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="37" ht="66" spans="1:19">
       <c r="A37" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D37" s="3"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
+      <c r="I37" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="Q37" s="1"/>
+      <c r="L37" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
     </row>
-    <row r="38" ht="27" spans="1:19">
+    <row r="38" ht="33" spans="1:19">
       <c r="A38" s="1" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38" s="3"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
+      <c r="I38" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
+      <c r="L38" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="Q38" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="R38" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S38" s="1">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="39" ht="49.5" spans="1:19">
+        <v>74</v>
+      </c>
+      <c r="R38" s="1"/>
+      <c r="S38" s="1"/>
+    </row>
+    <row r="39" ht="27" spans="1:19">
       <c r="A39" s="1" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" s="3"/>
-      <c r="G39" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H39" s="1">
-        <v>-448</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
       <c r="I39" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K39" s="1">
+        <v>100</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="Q39" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="S39" s="1">
-        <v>448</v>
+        <v>650</v>
       </c>
     </row>
     <row r="40" ht="49.5" spans="1:19">
       <c r="A40" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D40" s="3"/>
-      <c r="G40" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H40" s="1">
-        <v>-450</v>
-      </c>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
       <c r="I40" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
+      <c r="L40" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="Q40" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="R40" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S40" s="1">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="41" ht="33" spans="1:19">
+        <v>26</v>
+      </c>
+      <c r="R40" s="1"/>
+      <c r="S40" s="1"/>
+    </row>
+    <row r="41" ht="49.5" spans="1:19">
       <c r="A41" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D41" s="3"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
+      <c r="I41" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="Q41" s="1"/>
+      <c r="L41" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q41" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
     </row>
-    <row r="42" ht="66" spans="1:19">
+    <row r="42" ht="33" spans="1:19">
       <c r="A42" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" s="1"/>
-      <c r="D42" s="3" t="s">
-        <v>77</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D42" s="3"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
+      <c r="I42" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="Q42" s="1"/>
+      <c r="L42" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
     </row>
-    <row r="43" ht="33" spans="1:19">
+    <row r="43" ht="66" spans="1:19">
       <c r="A43" s="1" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C43" s="1"/>
-      <c r="D43" s="3"/>
+      <c r="D43" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
+      <c r="I43" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="Q43" s="1"/>
+      <c r="L43" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
     </row>
-    <row r="44" ht="82.5" spans="1:19">
+    <row r="44" ht="33" spans="1:19">
       <c r="A44" s="1" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>46</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="C44" s="1"/>
       <c r="D44" s="3"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
+      <c r="I44" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="Q44" s="1"/>
+      <c r="L44" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q44" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
     </row>
-    <row r="45" ht="33" spans="1:19">
+    <row r="45" ht="82.5" spans="1:19">
       <c r="A45" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C45" s="1"/>
-      <c r="D45" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D45" s="3"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
+      <c r="I45" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="Q45" s="1"/>
+      <c r="L45" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q45" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
     </row>
     <row r="46" ht="33" spans="1:19">
       <c r="A46" s="1" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C46" s="1"/>
-      <c r="D46" s="3" t="s">
-        <v>82</v>
+      <c r="D46" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
+      <c r="I46" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="Q46" s="1"/>
+      <c r="L46" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q46" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
     </row>
-    <row r="47" ht="16.5" spans="1:19">
+    <row r="47" ht="33" spans="1:19">
       <c r="A47" s="1" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D47" s="3"/>
+        <v>87</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="D47" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
+      <c r="I47" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="Q47" s="1"/>
+      <c r="L47" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q47" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
     </row>
     <row r="48" ht="16.5" spans="1:19">
-      <c r="A48" t="s">
-        <v>84</v>
-      </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="1"/>
+      <c r="A48" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="D48" s="3"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -2858,7 +3003,7 @@
     </row>
     <row r="49" ht="16.5" spans="1:19">
       <c r="A49" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
@@ -2872,7 +3017,7 @@
     </row>
     <row r="50" ht="16.5" spans="1:19">
       <c r="A50" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>

--- a/Assets/StreamingAssets/story/11.xlsx
+++ b/Assets/StreamingAssets/story/11.xlsx
@@ -94,7 +94,7 @@
     <t>narrator</t>
   </si>
   <si>
-    <t>雨下了整整三个小时。</t>
+    <t>Rain had fallen for three full hours.</t>
   </si>
   <si>
     <t>bk</t>
@@ -112,64 +112,64 @@
     <t>c</t>
   </si>
   <si>
-    <t>乡间宅邸的壁灯忽明忽暗，像一双困倦却不肯闭上的眼睛。</t>
-  </si>
-  <si>
-    <t>铜制挂钟停在九点十七分，又在下一声滴答里继续向前。</t>
+    <t>The wall lamps in the country estate flickered like a pair of weary eyes that refused to close.</t>
+  </si>
+  <si>
+    <t>The brass clock stopped at 9:17, then moved forward again with the next tick.</t>
   </si>
   <si>
     <t>Amb_Clock_Tick</t>
   </si>
   <si>
-    <t>雨水沿玻璃蜿蜒而下，把庭院里的玫瑰揉成一团模糊的暗红。</t>
+    <t>Rainwater wound its way down the glass, blurring the roses in the courtyard into a dark red haze.</t>
   </si>
   <si>
     <t>Amb_Thunderstorm</t>
   </si>
   <si>
-    <t>壁炉里只剩低伏的火，偶尔咬碎一截木炭。</t>
-  </si>
-  <si>
-    <t>长桌旁坐着四个人。没有人开口。</t>
+    <t>Only a low fire remained in the hearth, occasionally biting through a piece of charcoal.</t>
+  </si>
+  <si>
+    <t>Four people sat around the long table. No one spoke.</t>
   </si>
   <si>
     <t>appearAt</t>
   </si>
   <si>
-    <t>你坐在桌子的这一端，面前只有一只深棕色皮革档案袋。</t>
-  </si>
-  <si>
-    <t>Arthur Bell靠在椅背上，领带打得一丝不苟。</t>
+    <t>You sat at one end of the table with nothing before you but a dark brown leather case file.</t>
+  </si>
+  <si>
+    <t>Arthur Bell leaned back in his chair, his tie arranged with immaculate precision.</t>
   </si>
   <si>
     <t>a2</t>
   </si>
   <si>
-    <t>他用食指敲着扶手，仿佛今晚只是一次无聊的聚会。</t>
-  </si>
-  <si>
-    <t>看够了吗？</t>
+    <t>He tapped the armrest with his index finger, as though tonight were nothing more than a tedious gathering.</t>
+  </si>
+  <si>
+    <t>Had your fill?</t>
   </si>
   <si>
     <t>moveTo</t>
   </si>
   <si>
-    <t>Beatrice Hall坐得过分端正，只有交叠的手指出卖了颤抖。</t>
-  </si>
-  <si>
-    <t>我不知道你为什么把我们叫到这里。</t>
-  </si>
-  <si>
-    <t>Charles Reed坐在最远处，目光始终落在桌面的木纹上。</t>
+    <t>Beatrice Hall sat unnaturally straight, betrayed only by the trembling of her interlaced fingers.</t>
+  </si>
+  <si>
+    <t>I don't know why you brought us here.</t>
+  </si>
+  <si>
+    <t>Charles Reed sat farthest away, his gaze fixed on the grain of the wooden table.</t>
   </si>
   <si>
     <t>c2</t>
   </si>
   <si>
-    <t>……</t>
-  </si>
-  <si>
-    <t>你把档案袋拉到面前。三道视线终于落在了同一个地方。</t>
+    <t>...</t>
+  </si>
+  <si>
+    <t>You pulled the case file toward you. At last, all three pairs of eyes settled on the same place.</t>
   </si>
   <si>
     <t>BGM_Suspense_Loop</t>
@@ -178,28 +178,28 @@
     <t>u</t>
   </si>
   <si>
-    <t>九点十七分。和她死去的时间一样。</t>
-  </si>
-  <si>
-    <t>你约我们来这里，就是为了翻旧账？</t>
-  </si>
-  <si>
-    <t>我以为我们早就达成共识了。</t>
-  </si>
-  <si>
-    <t>我和你们，可没有什么共识。</t>
-  </si>
-  <si>
-    <t>你的拇指压住金属扣。</t>
-  </si>
-  <si>
-    <t>“咔哒”一声，皮扣松开。</t>
+    <t>Nine seventeen. The exact time she died.</t>
+  </si>
+  <si>
+    <t>You called us here just to drag up the past?</t>
+  </si>
+  <si>
+    <t>I thought we had reached an understanding long ago.</t>
+  </si>
+  <si>
+    <t>I never reached any understanding with you.</t>
+  </si>
+  <si>
+    <t>Your thumb pressed against the metal clasp.</t>
+  </si>
+  <si>
+    <t>With a click, the leather fastener came loose.</t>
   </si>
   <si>
     <t>UI_Flip_Card2</t>
   </si>
   <si>
-    <t>你从档案中抽出一张泛黄的照片，放在长桌中央。</t>
+    <t>You drew a yellowed photograph from the file and placed it in the middle of the long table.</t>
   </si>
   <si>
     <t>UI_Flip_Card1</t>
@@ -211,43 +211,43 @@
     <t>dead</t>
   </si>
   <si>
-    <t>照片里的 Clara 静静站着，垂落的黑发遮住了大半张脸。她微抿着唇，仿佛早已预感到那个夜晚终会到来。</t>
-  </si>
-  <si>
-    <t>Clara死前，见过你们三个人。</t>
-  </si>
-  <si>
-    <t>所以呢？见过我们，不等于我们杀了她。</t>
-  </si>
-  <si>
-    <t>我还没有说她是被杀的。</t>
-  </si>
-  <si>
-    <t>文字游戏。你还是只会这一套。</t>
-  </si>
-  <si>
-    <t>等一下……如果这是警方的调查，为什么没有警察？</t>
-  </si>
-  <si>
-    <t>又为什么偏偏是我们三个？</t>
-  </si>
-  <si>
-    <t>别装了，Beatrice。你收到消息时，可没有这么惊讶。</t>
-  </si>
-  <si>
-    <t>那条消息是你发的！你说Clara只是出了意外！</t>
-  </si>
-  <si>
-    <t>我说的是我看到的。至于后来发生了什么，你应该问Charles。</t>
-  </si>
-  <si>
-    <t>Charles？你后来又回去了？</t>
+    <t>In the photograph, Clara stood in silence, her dark hair falling across most of her face. Her lips were faintly pursed, as though she had always known that night would come.</t>
+  </si>
+  <si>
+    <t>Before Clara died, she saw all three of you.</t>
+  </si>
+  <si>
+    <t>So what? Seeing us doesn't mean we killed her.</t>
+  </si>
+  <si>
+    <t>I never said she was murdered.</t>
+  </si>
+  <si>
+    <t>Word games. That's still the only trick you know.</t>
+  </si>
+  <si>
+    <t>Wait... if this is a police investigation, why aren't the police here?</t>
+  </si>
+  <si>
+    <t>And why is it specifically the three of us?</t>
+  </si>
+  <si>
+    <t>Stop pretending, Beatrice. You weren't nearly this surprised when you received the message.</t>
+  </si>
+  <si>
+    <t>You sent that message! You said Clara had only had an accident!</t>
+  </si>
+  <si>
+    <t>I told you what I saw. If you want to know what happened afterward, you should ask Charles.</t>
+  </si>
+  <si>
+    <t>Charles? You went back afterward?</t>
   </si>
   <si>
     <t>b2</t>
   </si>
   <si>
-    <t>Charles的鞋尖向后挪了半寸。</t>
+    <t>The toe of Charles's shoe slid half an inch backward.</t>
   </si>
   <si>
     <t>UI_Stamp</t>
@@ -256,49 +256,49 @@
     <t>c3</t>
   </si>
   <si>
-    <t>回答她。你不是最擅长替别人收拾残局吗？</t>
-  </si>
-  <si>
-    <t>你还是和以前一样。</t>
+    <t>Answer her. Aren't you the one who's best at cleaning up other people's messes?</t>
+  </si>
+  <si>
+    <t>You're still the same as ever.</t>
   </si>
   <si>
     <t>system</t>
   </si>
   <si>
-    <t>（沉默）</t>
-  </si>
-  <si>
-    <t>够了。我们三个那晚都在场。</t>
-  </si>
-  <si>
-    <t>但最后一个离开的人，不是我。</t>
-  </si>
-  <si>
-    <t>你什么意思？</t>
-  </si>
-  <si>
-    <t>你翻开档案第一页。三个人同时安静下来。</t>
+    <t>(Silence)</t>
+  </si>
+  <si>
+    <t>Enough. All three of us were there that night.</t>
+  </si>
+  <si>
+    <t>But I wasn't the last one to leave.</t>
+  </si>
+  <si>
+    <t>What do you mean?</t>
+  </si>
+  <si>
+    <t>You opened the first page of the file. All three of them fell silent at once.</t>
   </si>
   <si>
     <t>UI_Page_Turn1</t>
   </si>
   <si>
-    <t>嫌疑人状态已建立。</t>
-  </si>
-  <si>
-    <t>今晚，我们不谈共识。只谈你们各自隐瞒的事实。</t>
-  </si>
-  <si>
-    <t>挂钟的分针越过刻度。</t>
-  </si>
-  <si>
-    <t>（钟声响起）</t>
+    <t>Suspect profiles established.</t>
+  </si>
+  <si>
+    <t>Tonight, we are not discussing any agreement. We are discussing the facts each of you has concealed.</t>
+  </si>
+  <si>
+    <t>The minute hand passed the next mark.</t>
+  </si>
+  <si>
+    <t>(The clock chimes.)</t>
   </si>
   <si>
     <t>SFX_Clock_Oneshot</t>
   </si>
   <si>
-    <t>审讯开始。</t>
+    <t>The interrogation begins.</t>
   </si>
   <si>
     <t>EOF</t>
@@ -314,7 +314,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -329,10 +329,22 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
     </font>
     <font>
       <u/>
@@ -479,7 +491,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -494,6 +506,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -679,7 +697,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -698,6 +716,21 @@
         <color rgb="FFD9D9D9"/>
       </top>
       <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="medium">
         <color rgb="FFD9D9D9"/>
       </bottom>
       <diagonal/>
@@ -820,150 +853,153 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1280,7 +1316,7 @@
   <dimension ref="A1:T50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" ht="14.25" spans="1:20">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1342,7 +1378,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" ht="33" spans="1:20">
+    <row r="2" ht="66.75" spans="1:20">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -1372,7 +1408,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" ht="99" spans="1:20">
+    <row r="3" ht="182.25" spans="1:20">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -1414,7 +1450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" ht="82.5" spans="1:20">
+    <row r="4" ht="149.25" spans="1:20">
       <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
@@ -1458,7 +1494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="99" spans="1:20">
+    <row r="5" ht="165.75" spans="1:20">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
@@ -1502,7 +1538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="66" spans="1:20">
+    <row r="6" ht="165.75" spans="1:20">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
@@ -1546,7 +1582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="49.5" spans="1:20">
+    <row r="7" ht="99.75" spans="1:20">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -1600,7 +1636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="82.5" spans="1:20">
+    <row r="8" ht="165.75" spans="1:20">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -1641,7 +1677,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="9" ht="82.5" spans="1:20">
+    <row r="9" ht="165.75" spans="1:20">
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
@@ -1682,7 +1718,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="10" ht="82.5" spans="1:20">
+    <row r="10" ht="215.25" spans="1:20">
       <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
@@ -1723,7 +1759,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="11" ht="16.5" spans="1:20">
+    <row r="11" ht="33.75" spans="1:20">
       <c r="A11" s="1" t="s">
         <v>24</v>
       </c>
@@ -1770,7 +1806,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="12" ht="99" spans="1:20">
+    <row r="12" ht="182.25" spans="1:20">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -1815,7 +1851,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="13" ht="66" spans="1:20">
+    <row r="13" ht="83.25" spans="1:20">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,7 +1894,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="14" ht="99" spans="1:20">
+    <row r="14" ht="165.75" spans="1:20">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,7 +1939,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="15" ht="16.5" spans="1:20">
+    <row r="15" ht="17.25" spans="1:20">
       <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
@@ -1946,7 +1982,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" ht="82.5" spans="1:20">
+    <row r="16" ht="165.75" spans="1:20">
       <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
@@ -1988,7 +2024,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="17" ht="66" spans="1:20">
+    <row r="17" ht="83.25" spans="1:20">
       <c r="A17" s="1" t="s">
         <v>48</v>
       </c>
@@ -2010,15 +2046,15 @@
         <v>25</v>
       </c>
       <c r="M17" t="str">
-        <f>IF(E16&lt;&gt;"",E16,M16)</f>
+        <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O17">
-        <f>IF(H16&lt;&gt;"",H16,O16)</f>
+        <f t="shared" si="1"/>
         <v>-650</v>
       </c>
       <c r="P17">
-        <f>IF(K16&lt;&gt;"",K16,P16)</f>
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="Q17" s="1" t="s">
@@ -2035,7 +2071,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="18" ht="66" spans="1:20">
+    <row r="18" ht="83.25" spans="1:20">
       <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
@@ -2078,7 +2114,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="19" ht="49.5" spans="1:20">
+    <row r="19" ht="116.25" spans="1:20">
       <c r="A19" s="1" t="s">
         <v>24</v>
       </c>
@@ -2121,7 +2157,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="20" ht="49.5" spans="1:20">
+    <row r="20" ht="99.75" spans="1:20">
       <c r="A20" s="1" t="s">
         <v>48</v>
       </c>
@@ -2164,7 +2200,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="21" ht="33" spans="1:20">
+    <row r="21" ht="99.75" spans="1:20">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -2205,7 +2241,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="22" ht="49.5" spans="1:20">
+    <row r="22" ht="99.75" spans="1:20">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -2248,7 +2284,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="23" ht="82.5" spans="1:20">
+    <row r="23" ht="149.25" spans="1:20">
       <c r="A23" s="1" t="s">
         <v>20</v>
       </c>
@@ -2291,15 +2327,15 @@
         <v>650</v>
       </c>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" ht="14.25" spans="1:20">
       <c r="A24" t="s">
         <v>58</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="25" ht="165" spans="1:20">
+    <row r="25" ht="347.25" spans="1:20">
       <c r="A25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2340,7 +2376,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="26" ht="49.5" spans="1:20">
+    <row r="26" ht="83.25" spans="1:20">
       <c r="A26" s="1" t="s">
         <v>48</v>
       </c>
@@ -2383,7 +2419,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="27" ht="66" spans="1:20">
+    <row r="27" ht="83.25" spans="1:20">
       <c r="A27" s="1" t="s">
         <v>24</v>
       </c>
@@ -2410,7 +2446,7 @@
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
     </row>
-    <row r="28" ht="49.5" spans="1:20">
+    <row r="28" ht="66.75" spans="1:20">
       <c r="A28" s="1" t="s">
         <v>48</v>
       </c>
@@ -2437,7 +2473,7 @@
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
     </row>
-    <row r="29" ht="49.5" spans="1:20">
+    <row r="29" ht="99.75" spans="1:20">
       <c r="A29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2468,7 +2504,7 @@
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
     </row>
-    <row r="30" ht="82.5" spans="1:20">
+    <row r="30" ht="132.75" spans="1:20">
       <c r="A30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2495,7 +2531,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
     </row>
-    <row r="31" ht="49.5" spans="1:20">
+    <row r="31" ht="83.25" spans="1:20">
       <c r="A31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2522,7 +2558,7 @@
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
     </row>
-    <row r="32" ht="82.5" spans="1:20">
+    <row r="32" ht="182.25" spans="1:20">
       <c r="A32" s="1" t="s">
         <v>24</v>
       </c>
@@ -2549,7 +2585,7 @@
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
     </row>
-    <row r="33" ht="82.5" spans="1:19">
+    <row r="33" ht="132.75" spans="1:19">
       <c r="A33" s="1" t="s">
         <v>25</v>
       </c>
@@ -2580,7 +2616,7 @@
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
     </row>
-    <row r="34" ht="99" spans="1:19">
+    <row r="34" ht="165.75" spans="1:19">
       <c r="A34" s="1" t="s">
         <v>24</v>
       </c>
@@ -2615,7 +2651,7 @@
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
     </row>
-    <row r="35" ht="49.5" spans="1:19">
+    <row r="35" ht="66.75" spans="1:19">
       <c r="A35" s="1" t="s">
         <v>25</v>
       </c>
@@ -2646,7 +2682,7 @@
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
     </row>
-    <row r="36" ht="49.5" spans="1:19">
+    <row r="36" ht="99.75" spans="1:19">
       <c r="A36" s="1" t="s">
         <v>20</v>
       </c>
@@ -2677,7 +2713,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="37" ht="66" spans="1:19">
+    <row r="37" ht="149.25" spans="1:19">
       <c r="A37" s="1" t="s">
         <v>24</v>
       </c>
@@ -2704,7 +2740,7 @@
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
     </row>
-    <row r="38" ht="33" spans="1:19">
+    <row r="38" ht="50.25" spans="1:19">
       <c r="A38" s="1" t="s">
         <v>26</v>
       </c>
@@ -2731,7 +2767,7 @@
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
     </row>
-    <row r="39" ht="27" spans="1:19">
+    <row r="39" ht="27.75" spans="1:19">
       <c r="A39" s="1" t="s">
         <v>77</v>
       </c>
@@ -2766,7 +2802,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="40" ht="49.5" spans="1:19">
+    <row r="40" ht="83.25" spans="1:19">
       <c r="A40" s="1" t="s">
         <v>24</v>
       </c>
@@ -2793,7 +2829,7 @@
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
     </row>
-    <row r="41" ht="49.5" spans="1:19">
+    <row r="41" ht="66.75" spans="1:19">
       <c r="A41" s="1" t="s">
         <v>24</v>
       </c>
@@ -2820,7 +2856,7 @@
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
     </row>
-    <row r="42" ht="33" spans="1:19">
+    <row r="42" ht="33.75" spans="1:19">
       <c r="A42" s="1" t="s">
         <v>25</v>
       </c>
@@ -2847,7 +2883,7 @@
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
     </row>
-    <row r="43" ht="66" spans="1:19">
+    <row r="43" ht="149.25" spans="1:19">
       <c r="A43" s="1" t="s">
         <v>20</v>
       </c>
@@ -2874,7 +2910,7 @@
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
     </row>
-    <row r="44" ht="33" spans="1:19">
+    <row r="44" ht="66.75" spans="1:19">
       <c r="A44" s="1" t="s">
         <v>77</v>
       </c>
@@ -2899,7 +2935,7 @@
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
     </row>
-    <row r="45" ht="82.5" spans="1:19">
+    <row r="45" ht="182.25" spans="1:19">
       <c r="A45" s="1" t="s">
         <v>48</v>
       </c>
@@ -2926,7 +2962,7 @@
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
     </row>
-    <row r="46" ht="33" spans="1:19">
+    <row r="46" ht="83.25" spans="1:19">
       <c r="A46" s="1" t="s">
         <v>20</v>
       </c>
@@ -2953,7 +2989,7 @@
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
     </row>
-    <row r="47" ht="33" spans="1:19">
+    <row r="47" ht="33.75" spans="1:19">
       <c r="A47" s="1" t="s">
         <v>77</v>
       </c>
@@ -2980,7 +3016,7 @@
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
     </row>
-    <row r="48" ht="16.5" spans="1:19">
+    <row r="48" ht="50.25" spans="1:19">
       <c r="A48" s="1" t="s">
         <v>48</v>
       </c>

--- a/Assets/StreamingAssets/story/11.xlsx
+++ b/Assets/StreamingAssets/story/11.xlsx
@@ -1473,7 +1473,7 @@
         <v>25</v>
       </c>
       <c r="M4" t="str">
-        <f t="shared" ref="M4:M25" si="0">IF(E3&lt;&gt;"",E3,M3)</f>
+        <f t="shared" ref="M4:M48" si="0">IF(E3&lt;&gt;"",E3,M3)</f>
         <v>bk</v>
       </c>
       <c r="O4">
@@ -2093,15 +2093,15 @@
         <v>25</v>
       </c>
       <c r="M18" t="str">
-        <f t="shared" ref="M18:M23" si="4">IF(E17&lt;&gt;"",E17,M17)</f>
+        <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O18">
-        <f t="shared" ref="O18:O23" si="5">IF(H17&lt;&gt;"",H17,O17)</f>
+        <f t="shared" ref="O18:O23" si="4">IF(H17&lt;&gt;"",H17,O17)</f>
         <v>-650</v>
       </c>
       <c r="P18">
-        <f t="shared" ref="P18:P23" si="6">IF(K17&lt;&gt;"",K17,P17)</f>
+        <f t="shared" ref="P18:P23" si="5">IF(K17&lt;&gt;"",K17,P17)</f>
         <v>100</v>
       </c>
       <c r="Q18" s="1" t="s">
@@ -2110,7 +2110,7 @@
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18">
-        <f t="shared" ref="T18:T23" si="7">IF(S17&lt;&gt;"",S17,T17)</f>
+        <f t="shared" ref="T18:T23" si="6">IF(S17&lt;&gt;"",S17,T17)</f>
         <v>650</v>
       </c>
     </row>
@@ -2136,15 +2136,15 @@
         <v>25</v>
       </c>
       <c r="M19" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
+      <c r="O19">
         <f t="shared" si="4"/>
-        <v>bk</v>
-      </c>
-      <c r="O19">
+        <v>-650</v>
+      </c>
+      <c r="P19">
         <f t="shared" si="5"/>
-        <v>-650</v>
-      </c>
-      <c r="P19">
-        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="Q19" s="1" t="s">
@@ -2153,7 +2153,7 @@
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>650</v>
       </c>
     </row>
@@ -2179,15 +2179,15 @@
         <v>25</v>
       </c>
       <c r="M20" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
+      <c r="O20">
         <f t="shared" si="4"/>
-        <v>bk</v>
-      </c>
-      <c r="O20">
+        <v>-650</v>
+      </c>
+      <c r="P20">
         <f t="shared" si="5"/>
-        <v>-650</v>
-      </c>
-      <c r="P20">
-        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="Q20" s="1" t="s">
@@ -2196,7 +2196,7 @@
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>650</v>
       </c>
     </row>
@@ -2220,15 +2220,15 @@
         <v>25</v>
       </c>
       <c r="M21" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
+      <c r="O21">
         <f t="shared" si="4"/>
-        <v>bk</v>
-      </c>
-      <c r="O21">
+        <v>-650</v>
+      </c>
+      <c r="P21">
         <f t="shared" si="5"/>
-        <v>-650</v>
-      </c>
-      <c r="P21">
-        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="Q21" s="1" t="s">
@@ -2237,7 +2237,7 @@
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
       <c r="T21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>650</v>
       </c>
     </row>
@@ -2263,15 +2263,15 @@
         <v>25</v>
       </c>
       <c r="M22" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
+      <c r="O22">
         <f t="shared" si="4"/>
-        <v>bk</v>
-      </c>
-      <c r="O22">
+        <v>-650</v>
+      </c>
+      <c r="P22">
         <f t="shared" si="5"/>
-        <v>-650</v>
-      </c>
-      <c r="P22">
-        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="Q22" s="1" t="s">
@@ -2280,7 +2280,7 @@
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
       <c r="T22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>650</v>
       </c>
     </row>
@@ -2306,15 +2306,15 @@
         <v>25</v>
       </c>
       <c r="M23" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
+      <c r="O23">
         <f t="shared" si="4"/>
-        <v>bk</v>
-      </c>
-      <c r="O23">
+        <v>-650</v>
+      </c>
+      <c r="P23">
         <f t="shared" si="5"/>
-        <v>-650</v>
-      </c>
-      <c r="P23">
-        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="Q23" s="1" t="s">
@@ -2323,16 +2323,20 @@
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
       <c r="T23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>650</v>
       </c>
     </row>
-    <row r="24" ht="14.25" spans="1:20">
+    <row r="24" spans="1:20">
       <c r="A24" t="s">
         <v>58</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>59</v>
+      </c>
+      <c r="M24" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
       </c>
     </row>
     <row r="25" ht="347.25" spans="1:20">
@@ -2355,7 +2359,7 @@
         <v>25</v>
       </c>
       <c r="M25" t="str">
-        <f>IF(E23&lt;&gt;"",E23,M23)</f>
+        <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O25">
@@ -2398,7 +2402,7 @@
         <v>25</v>
       </c>
       <c r="M26" t="str">
-        <f>IF(E25&lt;&gt;"",E25,M25)</f>
+        <f t="shared" si="0"/>
         <v>bk</v>
       </c>
       <c r="O26">
@@ -2440,6 +2444,10 @@
       <c r="L27" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="M27" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
       <c r="Q27" s="1" t="s">
         <v>26</v>
       </c>
@@ -2467,6 +2475,10 @@
       <c r="L28" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="M28" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
       <c r="Q28" s="1" t="s">
         <v>26</v>
       </c>
@@ -2497,6 +2509,10 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1" t="s">
         <v>25</v>
+      </c>
+      <c r="M29" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
       </c>
       <c r="Q29" s="1" t="s">
         <v>26</v>
@@ -2525,6 +2541,10 @@
       <c r="L30" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="M30" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
       <c r="Q30" s="1" t="s">
         <v>26</v>
       </c>
@@ -2552,6 +2572,10 @@
       <c r="L31" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="M31" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
       <c r="Q31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2579,6 +2603,10 @@
       <c r="L32" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="M32" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
       <c r="Q32" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,6 +2638,10 @@
       <c r="L33" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="M33" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
       <c r="Q33" s="1" t="s">
         <v>26</v>
       </c>
@@ -2644,6 +2676,10 @@
       </c>
       <c r="L34" s="1" t="s">
         <v>25</v>
+      </c>
+      <c r="M34" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
       </c>
       <c r="Q34" s="1" t="s">
         <v>26</v>
@@ -2676,6 +2712,10 @@
       <c r="L35" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="M35" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
       <c r="Q35" s="1" t="s">
         <v>26</v>
       </c>
@@ -2703,6 +2743,10 @@
       <c r="L36" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="M36" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
       <c r="Q36" s="1" t="s">
         <v>74</v>
       </c>
@@ -2734,6 +2778,10 @@
       <c r="L37" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="M37" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
       <c r="Q37" s="1" t="s">
         <v>74</v>
       </c>
@@ -2761,6 +2809,10 @@
       <c r="L38" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="M38" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
       <c r="Q38" s="1" t="s">
         <v>74</v>
       </c>
@@ -2791,6 +2843,10 @@
       </c>
       <c r="L39" s="1" t="s">
         <v>25</v>
+      </c>
+      <c r="M39" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
       </c>
       <c r="Q39" s="1" t="s">
         <v>26</v>
@@ -2823,6 +2879,10 @@
       <c r="L40" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="M40" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
       <c r="Q40" s="1" t="s">
         <v>26</v>
       </c>
@@ -2850,6 +2910,10 @@
       <c r="L41" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="M41" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
       <c r="Q41" s="1" t="s">
         <v>26</v>
       </c>
@@ -2877,6 +2941,10 @@
       <c r="L42" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="M42" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
       <c r="Q42" s="1" t="s">
         <v>26</v>
       </c>
@@ -2903,6 +2971,10 @@
       <c r="K43" s="1"/>
       <c r="L43" s="1" t="s">
         <v>25</v>
+      </c>
+      <c r="M43" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
       </c>
       <c r="Q43" s="1" t="s">
         <v>26</v>
@@ -2929,6 +3001,10 @@
       <c r="L44" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="M44" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
       <c r="Q44" s="1" t="s">
         <v>26</v>
       </c>
@@ -2956,6 +3032,10 @@
       <c r="L45" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="M45" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
       <c r="Q45" s="1" t="s">
         <v>26</v>
       </c>
@@ -2983,6 +3063,10 @@
       <c r="L46" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="M46" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
       <c r="Q46" s="1" t="s">
         <v>26</v>
       </c>
@@ -3009,6 +3093,10 @@
       <c r="K47" s="1"/>
       <c r="L47" s="1" t="s">
         <v>25</v>
+      </c>
+      <c r="M47" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
       </c>
       <c r="Q47" s="1" t="s">
         <v>26</v>
@@ -3033,6 +3121,10 @@
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
+      <c r="M48" t="str">
+        <f t="shared" si="0"/>
+        <v>bk</v>
+      </c>
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
